--- a/output/full_scan/batch_seq8_2026-07-17.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-17.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7610</v>
+        <v>7714</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>733.6470466634919</v>
+        <v>777.8797031160801</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2410</v>
+        <v>181.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.82194703497126</v>
+        <v>61.25203609548193</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>34.01987154547483</v>
+        <v>39.91522880371866</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.556928058803581</v>
+        <v>0.8879703116080079</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-37.22778095931341</v>
+        <v>4.682827141918123</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8033</v>
+        <v>7610</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>691.7751351429379</v>
+        <v>733.6470466634919</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>219</v>
+        <v>2410</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.91927596508706</v>
+        <v>56.82194703497126</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>42.1863234386756</v>
+        <v>34.01987154547483</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.2649971198920823</v>
+        <v>1.556928058803581</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>4.105417535428501</v>
+        <v>-37.22778095931341</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7828</v>
+        <v>8033</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>647.1522077130546</v>
+        <v>691.7751351429379</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1945</v>
+        <v>219</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>49.85640890409193</v>
+        <v>58.91927596508706</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.98391074211151</v>
+        <v>42.1863234386756</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.124537716269808</v>
+        <v>0.2649971198920823</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-33.05825178645344</v>
+        <v>4.105417535428501</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8016</v>
+        <v>6907</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>625.3906687532959</v>
+        <v>681.773686250003</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>40.26397298007533</v>
+        <v>74.99112718270831</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28.46901834601013</v>
+        <v>42.66059672731812</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.4688867098367256</v>
+        <v>0.277368625000302</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-7.157024577858744</v>
+        <v>7.394666080445631</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6949</v>
+        <v>7828</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>619.8073863800739</v>
+        <v>647.1522077130546</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1030</v>
+        <v>1945</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>64.30880868805896</v>
+        <v>49.85640890409193</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>41.38603880746758</v>
+        <v>25.98391074211151</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.378749766482798</v>
+        <v>1.124537716269808</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>10.96327164339252</v>
+        <v>-33.05825178645344</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8024</v>
+        <v>8016</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>616.9432064262901</v>
+        <v>625.3906687532959</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16.15</v>
+        <v>286</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.73176083045298</v>
+        <v>40.26397298007533</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>39.11714496939764</v>
+        <v>28.46901834601013</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5432236478040295</v>
+        <v>0.4688867098367256</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.0092007911806246</v>
+        <v>-7.157024577858744</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8046</v>
+        <v>6949</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>581.6031678133953</v>
+        <v>619.8073863800739</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1150</v>
+        <v>1030</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>53.22092601987357</v>
+        <v>64.30880868805896</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21.49761053365944</v>
+        <v>41.38603880746758</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.7874355391850534</v>
+        <v>1.378749766482798</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>6.690665819729475</v>
+        <v>10.96327164339252</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6957</v>
+        <v>8024</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>580.5355280044738</v>
+        <v>616.9432064262901</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>246.5</v>
+        <v>16.15</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>80.82876767103018</v>
+        <v>57.73176083045298</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>43.14251712831631</v>
+        <v>39.11714496939764</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.840126115678751</v>
+        <v>0.5432236478040295</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4.790432117082265</v>
+        <v>0.0092007911806246</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8028</v>
+        <v>8046</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>579.6946903673773</v>
+        <v>581.6031678133953</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>315</v>
+        <v>1150</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>51.13732569795678</v>
+        <v>53.22092601987357</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23.35415353969984</v>
+        <v>21.49761053365944</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.785447450474627</v>
+        <v>0.7874355391850534</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1804565129437989</v>
+        <v>6.690665819729475</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7734</v>
+        <v>6957</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>571.3085512120286</v>
+        <v>580.5355280044738</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2850</v>
+        <v>246.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>44.26622951929817</v>
+        <v>80.82876767103018</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.76255225959182</v>
+        <v>43.14251712831631</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.586978503567792</v>
+        <v>1.840126115678751</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.6848523256084889</v>
+        <v>4.790432117082265</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7715</v>
+        <v>8028</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>542.272209642117</v>
+        <v>579.6946903673773</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>35.6</v>
+        <v>315</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.47089294621343</v>
+        <v>51.13732569795678</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.92254140852189</v>
+        <v>23.35415353969984</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.2748107003992416</v>
+        <v>1.785447450474627</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.0791314671184115</v>
+        <v>0.1804565129437989</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7788</v>
+        <v>7734</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>539.2251843141898</v>
+        <v>571.3085512120286</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>235</v>
+        <v>2850</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45.0619625534063</v>
+        <v>44.26622951929817</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>24.0683419017518</v>
+        <v>14.76255225959182</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.062375008405059</v>
+        <v>1.586978503567792</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-2.692120633984912</v>
+        <v>0.6848523256084889</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6901</v>
+        <v>7715</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>534.4935684983323</v>
+        <v>542.272209642117</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>18.35</v>
+        <v>35.6</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>53.02110107019338</v>
+        <v>57.47089294621343</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46.52905955433607</v>
+        <v>41.92254140852189</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.977457771281856</v>
+        <v>0.2748107003992416</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.1819607771040141</v>
+        <v>-0.0791314671184115</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6870</v>
+        <v>7788</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>528.0042806776338</v>
+        <v>539.2251843141898</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>320</v>
+        <v>235</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.1057422056052</v>
+        <v>45.0619625534063</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.88242345161701</v>
+        <v>24.0683419017518</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.197571694732432</v>
+        <v>1.062375008405059</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.085230445420706</v>
+        <v>-2.692120633984912</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6967</v>
+        <v>6901</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>496.6338242864742</v>
+        <v>534.4935684983323</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>77.7</v>
+        <v>18.35</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.78864180888306</v>
+        <v>53.02110107019338</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16.72751559160601</v>
+        <v>46.52905955433607</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.570003704065773</v>
+        <v>0.977457771281856</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.8433927000015394</v>
+        <v>-0.1819607771040141</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7717</v>
+        <v>6870</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>467.6632652135082</v>
+        <v>528.0042806776338</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>438</v>
+        <v>320</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>40.40812844315319</v>
+        <v>61.1057422056052</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21.92757220834282</v>
+        <v>21.88242345161701</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8800588770156655</v>
+        <v>1.197571694732432</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>10.38200011014591</v>
+        <v>2.085230445420706</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8047</v>
+        <v>6967</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>464.8496632447161</v>
+        <v>496.6338242864742</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>43</v>
+        <v>77.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>39.5176040834443</v>
+        <v>58.78864180888306</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11.12983933183097</v>
+        <v>16.72751559160601</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3006726773554076</v>
+        <v>1.570003704065773</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.4404673920345123</v>
+        <v>0.8433927000015394</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7839</v>
+        <v>7717</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>455.0157798437914</v>
+        <v>467.6632652135082</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.2</v>
+        <v>438</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42.24655829773141</v>
+        <v>40.40812844315319</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>12.01273376732518</v>
+        <v>21.92757220834282</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.436537908920605</v>
+        <v>0.8800588770156655</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1947609416736662</v>
+        <v>10.38200011014591</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7712</v>
+        <v>8047</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>450.7853993869638</v>
+        <v>464.8496632447161</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>144.5</v>
+        <v>43</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>34.09273274909529</v>
+        <v>39.5176040834443</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.23310437370026</v>
+        <v>11.12983933183097</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5812454789205606</v>
+        <v>0.3006726773554076</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-7.114491410696034</v>
+        <v>-0.4404673920345123</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8021</v>
+        <v>7839</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>441.5367583992006</v>
+        <v>455.0157798437914</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>454.5</v>
+        <v>42.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>41.19294352607248</v>
+        <v>42.24655829773141</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15.17140175090678</v>
+        <v>12.01273376732518</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.404593077514442</v>
+        <v>0.436537908920605</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-11.22026331875319</v>
+        <v>0.1947609416736662</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8039</v>
+        <v>7712</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>436.518330632424</v>
+        <v>450.7853993869638</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>192.5</v>
+        <v>144.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>68.03616760327952</v>
+        <v>34.09273274909529</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.04585071738115</v>
+        <v>28.23310437370026</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3.927614082797432</v>
+        <v>0.5812454789205606</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5.446688231886732</v>
+        <v>-7.114491410696034</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6934</v>
+        <v>8021</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>420.4296440171261</v>
+        <v>441.5367583992006</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>79.5</v>
+        <v>454.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.20591658214792</v>
+        <v>41.19294352607248</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.08861438375024</v>
+        <v>15.17140175090678</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5341298383728089</v>
+        <v>0.404593077514442</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.656433518578393</v>
+        <v>-11.22026331875319</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6919</v>
+        <v>8039</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>414.5203296041308</v>
+        <v>436.518330632424</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>103.5</v>
+        <v>192.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.01201259447399</v>
+        <v>68.03616760327952</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.94157334490201</v>
+        <v>27.04585071738115</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.217902711866554</v>
+        <v>3.927614082797432</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.5797960666798634</v>
+        <v>5.446688231886732</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7722</v>
+        <v>6934</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>414.0172659610925</v>
+        <v>420.4296440171261</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>300</v>
+        <v>79.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45.36161250977857</v>
+        <v>63.20591658214792</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>30.22258599224021</v>
+        <v>24.08861438375024</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5853919933056386</v>
+        <v>0.5341298383728089</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-3.060187107424317</v>
+        <v>1.656433518578393</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7402</v>
+        <v>6919</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>409.9035580236279</v>
+        <v>414.5203296041308</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>117</v>
+        <v>103.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.62287009997718</v>
+        <v>50.01201259447399</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.72544818046558</v>
+        <v>18.94157334490201</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8903558023627861</v>
+        <v>1.217902711866554</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.2949731477246775</v>
+        <v>0.5797960666798634</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>7799</v>
+        <v>7722</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>405.3024771774698</v>
+        <v>414.0172659610925</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>415.5</v>
+        <v>300</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.49659956690322</v>
+        <v>45.36161250977857</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>32.84733120017021</v>
+        <v>30.22258599224021</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.249207208548529</v>
+        <v>0.5853919933056386</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.413139010143958</v>
+        <v>-3.060187107424317</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6951</v>
+        <v>7402</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>404.6326907705122</v>
+        <v>409.9035580236279</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>72.2</v>
+        <v>117</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>29.93541855548655</v>
+        <v>48.62287009997718</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>29.59534312321814</v>
+        <v>31.72544818046558</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.141538935321784</v>
+        <v>0.8903558023627861</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.5517601108645793</v>
+        <v>-0.2949731477246775</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7711</v>
+        <v>7799</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>403.9355987505206</v>
+        <v>405.3024771774698</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>295</v>
+        <v>415.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>31.98642716821647</v>
+        <v>53.49659956690322</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>25.04122044357488</v>
+        <v>32.84733120017021</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.192129935094417</v>
+        <v>1.249207208548529</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.2475819835274659</v>
+        <v>-1.413139010143958</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8042</v>
+        <v>6951</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>399.1775007750908</v>
+        <v>404.6326907705122</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>129.5</v>
+        <v>72.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>37.39559856177996</v>
+        <v>29.93541855548655</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.32240366393068</v>
+        <v>29.59534312321814</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7104590163592233</v>
+        <v>2.141538935321784</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-8.619199404721162</v>
+        <v>-0.5517601108645793</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7842</v>
+        <v>7711</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>392.0278562729259</v>
+        <v>403.9355987505206</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>92.7</v>
+        <v>295</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.66924612660783</v>
+        <v>31.98642716821647</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.31993829974608</v>
+        <v>25.04122044357488</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.227544990275626</v>
+        <v>1.192129935094417</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-2.905009257429866</v>
+        <v>-0.2475819835274659</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6937</v>
+        <v>8042</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>390.4353044651697</v>
+        <v>399.1775007750908</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>269</v>
+        <v>129.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>48.2705100331698</v>
+        <v>37.39559856177996</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11.93293666506658</v>
+        <v>21.32240366393068</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.785172591089716</v>
+        <v>0.7104590163592233</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.487752346871358</v>
+        <v>-8.619199404721162</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6914</v>
+        <v>7842</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>389.5517119084447</v>
+        <v>392.0278562729259</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>144</v>
+        <v>92.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.6694031843552</v>
+        <v>49.66924612660783</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13.04360178845061</v>
+        <v>20.31993829974608</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.295867009523397</v>
+        <v>1.227544990275626</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2132281061119056</v>
+        <v>-2.905009257429866</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6903</v>
+        <v>6937</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>383.9340385274793</v>
+        <v>390.4353044651697</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>362.5</v>
+        <v>269</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>43.44143577997979</v>
+        <v>48.2705100331698</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10.07928746292532</v>
+        <v>11.93293666506658</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.47778075160257</v>
+        <v>1.785172591089716</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.8025746041657358</v>
+        <v>1.487752346871358</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6983</v>
+        <v>6914</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>383.4437717873602</v>
+        <v>389.5517119084447</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>333</v>
+        <v>144</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>39.69186857082589</v>
+        <v>51.6694031843552</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10.03992302628526</v>
+        <v>13.04360178845061</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.522925646851268</v>
+        <v>2.295867009523397</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.106012806784987</v>
+        <v>0.2132281061119056</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8045</v>
+        <v>6903</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>380.3728121891469</v>
+        <v>383.9340385274793</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>55.8</v>
+        <v>362.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>38.78208743682649</v>
+        <v>43.44143577997979</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11.27774651039869</v>
+        <v>10.07928746292532</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.669540902724357</v>
+        <v>1.47778075160257</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0998724500947432</v>
+        <v>-0.8025746041657358</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7631</v>
+        <v>6983</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>379.2315357117959</v>
+        <v>383.4437717873602</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>138.5</v>
+        <v>333</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46.42537119610708</v>
+        <v>39.69186857082589</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.93974415447137</v>
+        <v>10.03992302628526</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.1653746893405305</v>
+        <v>1.522925646851268</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-2.978102593682731</v>
+        <v>-0.106012806784987</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8043</v>
+        <v>8045</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>378.9146520222682</v>
+        <v>380.3728121891469</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>141</v>
+        <v>55.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>35.79953042579993</v>
+        <v>38.78208743682649</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23.20461019717069</v>
+        <v>11.27774651039869</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4643295793976449</v>
+        <v>1.669540902724357</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-8.200677369304831</v>
+        <v>0.0998724500947432</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6916</v>
+        <v>7631</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>375.9411864174093</v>
+        <v>379.2315357117959</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>19.45</v>
+        <v>138.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45.25093304532709</v>
+        <v>46.42537119610708</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.97003220120706</v>
+        <v>13.93974415447137</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8490597736606558</v>
+        <v>0.1653746893405305</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1598404791284795</v>
+        <v>-2.978102593682731</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7728</v>
+        <v>8043</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>374.4041048675848</v>
+        <v>378.9146520222682</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>642</v>
+        <v>141</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>41.47242292245276</v>
+        <v>35.79953042579993</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10.9224371247005</v>
+        <v>23.20461019717069</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9079764035488652</v>
+        <v>0.4643295793976449</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.275827329736757</v>
+        <v>-8.200677369304831</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8040</v>
+        <v>6916</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>370.7665626358082</v>
+        <v>375.9411864174093</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>19.45</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>31.68315056599322</v>
+        <v>45.25093304532709</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>24.63775813846934</v>
+        <v>14.97003220120706</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3589067514551601</v>
+        <v>0.8490597736606558</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.12969980249198</v>
+        <v>-0.1598404791284795</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6944</v>
+        <v>7728</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>358.6472201609073</v>
+        <v>374.4041048675848</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>976</v>
+        <v>642</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.5622945404852</v>
+        <v>41.47242292245276</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11.3767910719901</v>
+        <v>10.9224371247005</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.123724839290923</v>
+        <v>0.9079764035488652</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.057144924941934</v>
+        <v>2.275827329736757</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6887</v>
+        <v>8040</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>354.2435223647672</v>
+        <v>370.7665626358082</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>39.45</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>59.90066267204553</v>
+        <v>31.68315056599322</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13.22298426209214</v>
+        <v>24.63775813846934</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.324352236476717</v>
+        <v>0.3589067514551601</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.5064604555322489</v>
+        <v>-3.12969980249198</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7818</v>
+        <v>6944</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>353.5875168642674</v>
+        <v>358.6472201609073</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>976</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.79184906300024</v>
+        <v>48.5622945404852</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.29120174995005</v>
+        <v>11.3767910719901</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6474713913091474</v>
+        <v>1.123724839290923</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.8533790146850746</v>
+        <v>-1.057144924941934</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6863</v>
+        <v>6887</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>353.4796002972189</v>
+        <v>354.2435223647672</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>39.45</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.9138031443512</v>
+        <v>59.90066267204553</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.208628258771</v>
+        <v>13.22298426209214</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.418763924652883</v>
+        <v>1.324352236476717</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.624707663818745</v>
+        <v>0.5064604555322489</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7792</v>
+        <v>7818</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>340.8286333736637</v>
+        <v>353.5875168642674</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>208.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>27.04483566201002</v>
+        <v>49.79184906300024</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.3758297615378</v>
+        <v>25.29120174995005</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.587247269086508</v>
+        <v>0.6474713913091474</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.599973329186266</v>
+        <v>0.8533790146850746</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6869</v>
+        <v>6863</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>340.7657662143366</v>
+        <v>353.4796002972189</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>66.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>31.9683073223871</v>
+        <v>51.9138031443512</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.75296620121556</v>
+        <v>25.208628258771</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.428183113037616</v>
+        <v>1.418763924652883</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.08659376264995219</v>
+        <v>1.624707663818745</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6928</v>
+        <v>7792</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>340.5706367971989</v>
+        <v>340.8286333736637</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>49.1</v>
+        <v>208.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>44.79171004946278</v>
+        <v>27.04483566201002</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>30.75440903893059</v>
+        <v>23.3758297615378</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6876668235299286</v>
+        <v>2.587247269086508</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.474510899150615</v>
+        <v>-2.599973329186266</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7823</v>
+        <v>6869</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>333.740579920211</v>
+        <v>340.7657662143366</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>83.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.24977817639063</v>
+        <v>31.9683073223871</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.33379618399787</v>
+        <v>22.75296620121556</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9526278504597748</v>
+        <v>1.428183113037616</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.8920554839401995</v>
+        <v>-0.08659376264995219</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6899</v>
+        <v>6928</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>330.2499287768182</v>
+        <v>340.5706367971989</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>50.8</v>
+        <v>49.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>25.17579326560177</v>
+        <v>44.79171004946278</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.15127919113072</v>
+        <v>30.75440903893059</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.330919222857603</v>
+        <v>0.6876668235299286</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.7106719383376137</v>
+        <v>-0.474510899150615</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7768</v>
+        <v>7823</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>330.1606287538881</v>
+        <v>333.740579920211</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>303</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>31.6497560390818</v>
+        <v>48.24977817639063</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.28551493993007</v>
+        <v>26.33379618399787</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.251412511227654</v>
+        <v>0.9526278504597748</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-2.705065364690562</v>
+        <v>0.8920554839401995</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8032</v>
+        <v>6899</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>325.7317511007021</v>
+        <v>330.2499287768182</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>36.3</v>
+        <v>50.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>26.60563803597246</v>
+        <v>25.17579326560177</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24.04749137043073</v>
+        <v>21.15127919113072</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.030183796861918</v>
+        <v>1.330919222857603</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.744624334493899</v>
+        <v>-0.7106719383376137</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7749</v>
+        <v>7768</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>324.7948545618345</v>
+        <v>330.1606287538881</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>358.5</v>
+        <v>303</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>26.49587815285162</v>
+        <v>31.6497560390818</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>20.30210667107561</v>
+        <v>22.28551493993007</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.997423258160789</v>
+        <v>1.251412511227654</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-4.930743272007536</v>
+        <v>-2.705065364690562</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6994</v>
+        <v>8032</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>324.6391431197161</v>
+        <v>325.7317511007021</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>39.45</v>
+        <v>36.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>29.06575819110592</v>
+        <v>26.60563803597246</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.5587740345381</v>
+        <v>24.04749137043073</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3746181527118967</v>
+        <v>1.030183796861918</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0546750920491456</v>
+        <v>-0.744624334493899</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6862</v>
+        <v>7749</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>323.7671624448181</v>
+        <v>324.7948545618345</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>154</v>
+        <v>358.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>34.46251612073556</v>
+        <v>26.49587815285162</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.79199698105904</v>
+        <v>20.30210667107561</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5718676238562667</v>
+        <v>0.997423258160789</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-4.19764270771293</v>
+        <v>-4.930743272007536</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7760</v>
+        <v>6994</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>323.6190549172496</v>
+        <v>324.6391431197161</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>34.2</v>
+        <v>39.45</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.31171707782181</v>
+        <v>29.06575819110592</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>28.39529057696433</v>
+        <v>30.5587740345381</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4632638756133307</v>
+        <v>0.3746181527118967</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0753509467093493</v>
+        <v>-0.0546750920491456</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6906</v>
+        <v>6862</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>323.3155888881433</v>
+        <v>323.7671624448181</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>70.3</v>
+        <v>154</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>26.97752960444388</v>
+        <v>34.46251612073556</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.92794370074951</v>
+        <v>16.79199698105904</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6801690630589222</v>
+        <v>0.5718676238562667</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-2.203695261715068</v>
+        <v>-4.19764270771293</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6996</v>
+        <v>7760</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>319.3031780458815</v>
+        <v>323.6190549172496</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>171</v>
+        <v>34.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>32.63380290288926</v>
+        <v>50.31171707782181</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.9170206361919</v>
+        <v>28.39529057696433</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.004390842949164</v>
+        <v>0.4632638756133307</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-2.976053235228026</v>
+        <v>-0.0753509467093493</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7791</v>
+        <v>6906</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>318.3101468050123</v>
+        <v>323.3155888881433</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>63.6</v>
+        <v>70.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.28218299640787</v>
+        <v>26.97752960444388</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.08394324196367</v>
+        <v>21.92794370074951</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.9661573924221932</v>
+        <v>0.6801690630589222</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2525880342794587</v>
+        <v>-2.203695261715068</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7769</v>
+        <v>6996</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>317.5083931369302</v>
+        <v>319.3031780458815</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>6070</v>
+        <v>171</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.73268277271213</v>
+        <v>32.63380290288926</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.57837620585071</v>
+        <v>20.9170206361919</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.081252358827347</v>
+        <v>1.004390842949164</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-39.07955652555647</v>
+        <v>-2.976053235228026</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7820</v>
+        <v>7791</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>317.0244460467937</v>
+        <v>318.3101468050123</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>110.5</v>
+        <v>63.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>36.37353023340526</v>
+        <v>54.28218299640787</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17.18935970734896</v>
+        <v>13.08394324196367</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.898913762343199</v>
+        <v>0.9661573924221932</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3039553910979022</v>
+        <v>0.2525880342794587</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6953</v>
+        <v>7769</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>315.5387891096792</v>
+        <v>317.5083931369302</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>217.5</v>
+        <v>6070</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.85138193198797</v>
+        <v>40.73268277271213</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10.83558136847946</v>
+        <v>12.57837620585071</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.353321468516908</v>
+        <v>1.081252358827347</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.6425814131125387</v>
+        <v>-39.07955652555647</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6877</v>
+        <v>7820</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>313.8781480366377</v>
+        <v>317.0244460467937</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>125</v>
+        <v>110.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>41.73043772162375</v>
+        <v>36.37353023340526</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.89307279416255</v>
+        <v>17.18935970734896</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3329596221676962</v>
+        <v>0.898913762343199</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.8671474866801088</v>
+        <v>0.3039553910979022</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7744</v>
+        <v>6953</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>313.0699775521676</v>
+        <v>315.5387891096792</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>428</v>
+        <v>217.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>35.78929362148155</v>
+        <v>38.85138193198797</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.84881534629787</v>
+        <v>10.83558136847946</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.9107324063800616</v>
+        <v>1.353321468516908</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3820335539332156</v>
+        <v>-0.6425814131125387</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7740</v>
+        <v>6877</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>312.6688549446026</v>
+        <v>313.8781480366377</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.32793235244805</v>
+        <v>41.73043772162375</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.28657088840775</v>
+        <v>12.89307279416255</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.24096636555063</v>
+        <v>0.3329596221676962</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.692007435472305</v>
+        <v>0.8671474866801088</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7827</v>
+        <v>7744</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>308.462568747035</v>
+        <v>313.0699775521676</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>159</v>
+        <v>428</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.98280013187439</v>
+        <v>35.78929362148155</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.80591747076961</v>
+        <v>10.84881534629787</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.376685540649944</v>
+        <v>0.9107324063800616</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.441611645730474</v>
+        <v>-0.3820335539332156</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6861</v>
+        <v>7740</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>306.2906924104146</v>
+        <v>312.6688549446026</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>225</v>
+        <v>153</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>29.86599348945653</v>
+        <v>47.32793235244805</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.86717309250064</v>
+        <v>16.28657088840775</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.8910628162696628</v>
+        <v>1.24096636555063</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-9.012251115941105</v>
+        <v>1.692007435472305</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6894</v>
+        <v>7827</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>305.9431114530558</v>
+        <v>308.462568747035</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>318.5</v>
+        <v>159</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>34.42036490158829</v>
+        <v>46.98280013187439</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.46316556684141</v>
+        <v>19.80591747076961</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.661919881187756</v>
+        <v>0.376685540649944</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-3.625497405178861</v>
+        <v>-1.441611645730474</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7786</v>
+        <v>6861</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>304.3064693862485</v>
+        <v>306.2906924104146</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>127.5</v>
+        <v>225</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.75270563149694</v>
+        <v>29.86599348945653</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.25247026167336</v>
+        <v>19.86717309250064</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.086721272105298</v>
+        <v>0.8910628162696628</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4620004159912667</v>
+        <v>-9.012251115941105</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7750</v>
+        <v>6894</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>303.6705479733229</v>
+        <v>305.9431114530558</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1815</v>
+        <v>318.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>32.47002850119934</v>
+        <v>34.42036490158829</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.23918495935968</v>
+        <v>15.46316556684141</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.105082026269868</v>
+        <v>1.661919881187756</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-19.05862009992104</v>
+        <v>-3.625497405178861</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7810</v>
+        <v>7786</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>303.4831334740063</v>
+        <v>304.3064693862485</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>195</v>
+        <v>127.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37.21521997946662</v>
+        <v>50.75270563149694</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.97305963924404</v>
+        <v>16.25247026167336</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.037651751169437</v>
+        <v>1.086721272105298</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2214940585594256</v>
+        <v>0.4620004159912667</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7556</v>
+        <v>7750</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>300.7575124661371</v>
+        <v>303.6705479733229</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>218.5</v>
+        <v>1815</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>25.41407136709016</v>
+        <v>32.47002850119934</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.01778637842323</v>
+        <v>17.23918495935968</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8563455504372789</v>
+        <v>1.105082026269868</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-7.014529881970159</v>
+        <v>-19.05862009992104</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6913</v>
+        <v>7810</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>297.5337575307839</v>
+        <v>303.4831334740063</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>119.5</v>
+        <v>195</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.59208654138901</v>
+        <v>37.21521997946662</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.14570379467335</v>
+        <v>14.97305963924404</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.158003232165209</v>
+        <v>1.037651751169437</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.4700223884701249</v>
+        <v>0.2214940585594256</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6910</v>
+        <v>7556</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>297.4900543148257</v>
+        <v>300.7575124661371</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>24.6</v>
+        <v>218.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>21.77054575900914</v>
+        <v>25.41407136709016</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.50977828341807</v>
+        <v>21.01778637842323</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2.307802927895539</v>
+        <v>0.8563455504372789</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2123547840281163</v>
+        <v>-7.014529881970159</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7751</v>
+        <v>6913</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>294.3525336986145</v>
+        <v>297.5337575307839</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1130</v>
+        <v>119.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>35.60802732359748</v>
+        <v>40.59208654138901</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.86161818363515</v>
+        <v>14.14570379467335</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6027901713832526</v>
+        <v>1.158003232165209</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-14.07198808258981</v>
+        <v>0.4700223884701249</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7805</v>
+        <v>6910</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>291.1837421543377</v>
+        <v>297.4900543148257</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>601</v>
+        <v>24.6</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>26.3375111732808</v>
+        <v>21.77054575900914</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>36.09260461793638</v>
+        <v>23.50977828341807</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.01005747998519</v>
+        <v>2.307802927895539</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-3.240086466903733</v>
+        <v>-0.2123547840281163</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6909</v>
+        <v>7751</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>288.0917915055259</v>
+        <v>294.3525336986145</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>43.9</v>
+        <v>1130</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>34.23634829956836</v>
+        <v>35.60802732359748</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.32767053568978</v>
+        <v>13.86161818363515</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.446906599582108</v>
+        <v>0.6027901713832526</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.398764278301388</v>
+        <v>-14.07198808258981</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7822</v>
+        <v>7805</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>287.9508547929968</v>
+        <v>291.1837421543377</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>874</v>
+        <v>601</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>34.83420791365421</v>
+        <v>26.3375111732808</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.40412041643635</v>
+        <v>36.09260461793638</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7793540937669415</v>
+        <v>1.01005747998519</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-19.52821347724809</v>
+        <v>-3.240086466903733</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7821</v>
+        <v>6909</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>283.0231070776433</v>
+        <v>288.0917915055259</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>40</v>
+        <v>43.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.06094885784854</v>
+        <v>34.23634829956836</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>28.50798605063485</v>
+        <v>18.32767053568978</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.88355346544976</v>
+        <v>0.446906599582108</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0292897827541374</v>
+        <v>-1.398764278301388</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6955</v>
+        <v>7822</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>282.2573446214777</v>
+        <v>287.9508547929968</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>112</v>
+        <v>874</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.99855004189873</v>
+        <v>34.83420791365421</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6.298636010235983</v>
+        <v>18.40412041643635</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.892851078754207</v>
+        <v>0.7793540937669415</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.7956432320531466</v>
+        <v>-19.52821347724809</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6890</v>
+        <v>7821</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>273.2288254460236</v>
+        <v>283.0231070776433</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.77951887396139</v>
+        <v>34.06094885784854</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.33729704592763</v>
+        <v>28.50798605063485</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.152365936699899</v>
+        <v>0.88355346544976</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-5.823266157126256</v>
+        <v>0.0292897827541374</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7772</v>
+        <v>6955</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>263.9171485086184</v>
+        <v>282.2573446214777</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>112</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>28.096586085352</v>
+        <v>46.99855004189873</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.49111189187441</v>
+        <v>6.298636010235983</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.296642298531051</v>
+        <v>1.892851078754207</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-2.05924342567741</v>
+        <v>0.7956432320531466</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6885</v>
+        <v>6890</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>255.0575207172744</v>
+        <v>273.2288254460236</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>20.75</v>
+        <v>173</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.84516147709801</v>
+        <v>36.77951887396139</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.07398640958522</v>
+        <v>18.33729704592763</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.426630439159208</v>
+        <v>1.152365936699899</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0015136262449671</v>
+        <v>-5.823266157126256</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6958</v>
+        <v>7772</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>250.4612051078134</v>
+        <v>263.9171485086184</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>18</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>59.45017956093304</v>
+        <v>28.096586085352</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.09427453118768</v>
+        <v>15.49111189187441</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.589548571501437</v>
+        <v>2.296642298531051</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1751059128117897</v>
+        <v>-2.05924342567741</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6859</v>
+        <v>6885</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>248.0484241604035</v>
+        <v>255.0575207172744</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>98</v>
+        <v>20.75</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>23.621130547611</v>
+        <v>39.84516147709801</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>23.57383166557496</v>
+        <v>15.07398640958522</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.13251114656195</v>
+        <v>1.426630439159208</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-2.756445948135546</v>
+        <v>0.0015136262449671</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7780</v>
+        <v>6958</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>246.1469577818743</v>
+        <v>250.4612051078134</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>35.16143612188347</v>
+        <v>59.45017956093304</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.98165101834237</v>
+        <v>18.09427453118768</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2.076002387710947</v>
+        <v>1.589548571501437</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0490851559421079</v>
+        <v>0.1751059128117897</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6855</v>
+        <v>6859</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>245.5563145615414</v>
+        <v>248.0484241604035</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.65980470460462</v>
+        <v>23.621130547611</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.677506853744138</v>
+        <v>23.57383166557496</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.898192197906756</v>
+        <v>1.13251114656195</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1433928201472021</v>
+        <v>-2.756445948135546</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7732</v>
+        <v>7780</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>245.5397132465202</v>
+        <v>246.1469577818743</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>35.65</v>
+        <v>17.3</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.73773386883901</v>
+        <v>35.16143612188347</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8.544055749333703</v>
+        <v>17.98165101834237</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5356078814699758</v>
+        <v>2.076002387710947</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.7113667735022968</v>
+        <v>-0.0490851559421079</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7730</v>
+        <v>6855</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>243.0685318248857</v>
+        <v>245.5563145615414</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.55882883736214</v>
+        <v>50.65980470460462</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.26915907226481</v>
+        <v>8.677506853744138</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.118342311373557</v>
+        <v>1.898192197906756</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.073937944147313</v>
+        <v>-0.1433928201472021</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7704</v>
+        <v>7732</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>241.1557504780386</v>
+        <v>245.5397132465202</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>53</v>
+        <v>35.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>29.40761496293432</v>
+        <v>51.73773386883901</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.6049617664699</v>
+        <v>8.544055749333703</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8275298609789568</v>
+        <v>0.5356078814699758</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.9760642666750112</v>
+        <v>0.7113667735022968</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6997</v>
+        <v>7730</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>241.1431131512421</v>
+        <v>243.0685318248857</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>168</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.7976874666907</v>
+        <v>38.55882883736214</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>8.883955167732903</v>
+        <v>12.26915907226481</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6775426375464487</v>
+        <v>1.118342311373557</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0444811588947406</v>
+        <v>-1.073937944147313</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7753</v>
+        <v>7704</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>240.9054684772514</v>
+        <v>241.1557504780386</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>40.2</v>
+        <v>53</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.2342440309407</v>
+        <v>29.40761496293432</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.96221631546818</v>
+        <v>17.6049617664699</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3976248381015193</v>
+        <v>0.8275298609789568</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2800864191428032</v>
+        <v>-0.9760642666750112</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6922</v>
+        <v>6997</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>239.5116580049748</v>
+        <v>241.1431131512421</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>164.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.65129739960821</v>
+        <v>49.7976874666907</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.22419852694642</v>
+        <v>8.883955167732903</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9554003838458084</v>
+        <v>0.6775426375464487</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.9867117342002129</v>
+        <v>-0.0444811588947406</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7747</v>
+        <v>7753</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>237.8421812115389</v>
+        <v>240.9054684772514</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>113</v>
+        <v>40.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>38.78896562037912</v>
+        <v>38.2342440309407</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.62281248815054</v>
+        <v>22.96221631546818</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.0887780182691954</v>
+        <v>0.3976248381015193</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-2.121791034032479</v>
+        <v>-0.2800864191428032</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6902</v>
+        <v>6922</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>236.8563723503136</v>
+        <v>239.5116580049748</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>125</v>
+        <v>164.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.61774941086839</v>
+        <v>35.65129739960821</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.36097021134868</v>
+        <v>14.22419852694642</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3735928533910126</v>
+        <v>0.9554003838458084</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.148208921865</v>
+        <v>-0.9867117342002129</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6952</v>
+        <v>7747</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>236.1218629548525</v>
+        <v>237.8421812115389</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>35.75</v>
+        <v>113</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.46519364766307</v>
+        <v>38.78896562037912</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.72388035695315</v>
+        <v>11.62281248815054</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.096704221704222</v>
+        <v>0.0887780182691954</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.07780210673637369</v>
+        <v>-2.121791034032479</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7721</v>
+        <v>6902</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>232.4898741735092</v>
+        <v>236.8563723503136</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>61.8</v>
+        <v>125</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>31.64445016584003</v>
+        <v>42.61774941086839</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.97866724465666</v>
+        <v>15.36097021134868</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8350552755056724</v>
+        <v>0.3735928533910126</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.8606785415135707</v>
+        <v>-1.148208921865</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6873</v>
+        <v>6952</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>230.6059015192584</v>
+        <v>236.1218629548525</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>35.75</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.16651471802858</v>
+        <v>49.46519364766307</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.90145494572729</v>
+        <v>13.72388035695315</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.219392306790604</v>
+        <v>1.096704221704222</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1031052559232459</v>
+        <v>0.07780210673637369</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6965</v>
+        <v>7721</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>229.2955311830303</v>
+        <v>232.4898741735092</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>79</v>
+        <v>61.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.62717144047986</v>
+        <v>31.64445016584003</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>26.01466874444409</v>
+        <v>11.97866724465666</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.691334570259333</v>
+        <v>0.8350552755056724</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1381963008109616</v>
+        <v>-0.8606785415135707</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6923</v>
+        <v>6873</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>229.2262781966123</v>
+        <v>230.6059015192584</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>76.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>48.07982494963337</v>
+        <v>43.16651471802858</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12.827444371843</v>
+        <v>15.90145494572729</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8556814301332688</v>
+        <v>1.219392306790604</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.3061308205081807</v>
+        <v>0.1031052559232459</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7770</v>
+        <v>6965</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>228.7983125425014</v>
+        <v>229.2955311830303</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>41.4</v>
+        <v>79</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.6754694017603</v>
+        <v>47.62717144047986</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6.535557910285215</v>
+        <v>26.01466874444409</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.543649551475257</v>
+        <v>0.691334570259333</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0474274713988967</v>
+        <v>0.1381963008109616</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6924</v>
+        <v>6923</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>215.5703231687811</v>
+        <v>229.2262781966123</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>113</v>
+        <v>76.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.61605970161586</v>
+        <v>48.07982494963337</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.49015717868232</v>
+        <v>12.827444371843</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3325972672619508</v>
+        <v>0.8556814301332688</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.6377377104487461</v>
+        <v>0.3061308205081807</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7705</v>
+        <v>7770</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>210.8636010703172</v>
+        <v>228.7983125425014</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>30.45</v>
+        <v>41.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.7988846994596</v>
+        <v>44.6754694017603</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.94214434103238</v>
+        <v>6.535557910285215</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7406618007734941</v>
+        <v>2.543649551475257</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0844556627127338</v>
+        <v>-0.0474274713988967</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7738</v>
+        <v>6924</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>209.2611016321774</v>
+        <v>215.5703231687811</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>168</v>
+        <v>113</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46.95748477609932</v>
+        <v>40.61605970161586</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.24084160645341</v>
+        <v>13.49015717868232</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7052762527337579</v>
+        <v>0.3325972672619508</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0611542571874401</v>
+        <v>-0.6377377104487461</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6936</v>
+        <v>7705</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>208.3586760401384</v>
+        <v>210.8636010703172</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>31.75</v>
+        <v>30.45</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.04006947433831</v>
+        <v>40.7988846994596</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.48542165250897</v>
+        <v>17.94214434103238</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.066672744256973</v>
+        <v>0.7406618007734941</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0407810605311268</v>
+        <v>-0.0844556627127338</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6854</v>
+        <v>7738</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>206.9101989028563</v>
+        <v>209.2611016321774</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>25.60419269764867</v>
+        <v>46.95748477609932</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>30.32452625983734</v>
+        <v>24.24084160645341</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.252418188238541</v>
+        <v>0.7052762527337579</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.9197177239771106</v>
+        <v>-0.0611542571874401</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7703</v>
+        <v>6936</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>203.2646457371816</v>
+        <v>208.3586760401384</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>186</v>
+        <v>31.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.19882510415903</v>
+        <v>37.04006947433831</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.27530532076387</v>
+        <v>15.48542165250897</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.357590776395028</v>
+        <v>2.066672744256973</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.7506906753660818</v>
+        <v>-0.0407810605311268</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8034</v>
+        <v>6854</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>202.5170663127473</v>
+        <v>206.9101989028563</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>19.15</v>
+        <v>103</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>17.79480345891777</v>
+        <v>25.60419269764867</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>31.30026788865523</v>
+        <v>30.32452625983734</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.033987987911578</v>
+        <v>1.252418188238541</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.2282365855667867</v>
+        <v>-0.9197177239771106</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6895</v>
+        <v>7703</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>199.9541805857492</v>
+        <v>203.2646457371816</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>124.5</v>
+        <v>186</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>27.52679596305623</v>
+        <v>39.19882510415903</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>26.63414209017569</v>
+        <v>11.27530532076387</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.580235748920308</v>
+        <v>1.357590776395028</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.969095557930812</v>
+        <v>-0.7506906753660818</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7765</v>
+        <v>8034</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>199.8894997588204</v>
+        <v>202.5170663127473</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>222.5</v>
+        <v>19.15</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.86795233700772</v>
+        <v>17.79480345891777</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.48462077224025</v>
+        <v>31.30026788865523</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9231752246398864</v>
+        <v>1.033987987911578</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.7918060396353006</v>
+        <v>-0.2282365855667867</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6988</v>
+        <v>6895</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>197.9058076746566</v>
+        <v>199.9541805857492</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>12.8</v>
+        <v>124.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>30.0691388877464</v>
+        <v>27.52679596305623</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.5405906935698</v>
+        <v>26.63414209017569</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.197885950859642</v>
+        <v>0.580235748920308</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.008311219464045699</v>
+        <v>-1.969095557930812</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6971</v>
+        <v>7765</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>197.3770532533116</v>
+        <v>199.8894997588204</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>26.75</v>
+        <v>222.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.79252213082316</v>
+        <v>41.86795233700772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.3091877474428</v>
+        <v>16.48462077224025</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.352590571254174</v>
+        <v>0.9231752246398864</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0780330140311286</v>
+        <v>0.7918060396353006</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6962</v>
+        <v>6988</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>193.4218228601752</v>
+        <v>197.9058076746566</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>32.45</v>
+        <v>12.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>34.51267856247044</v>
+        <v>30.0691388877464</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.67596239428818</v>
+        <v>11.5405906935698</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8876050260739308</v>
+        <v>2.197885950859642</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.6120074579245922</v>
+        <v>0.008311219464045699</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7547</v>
+        <v>6971</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>188.7758645614698</v>
+        <v>197.3770532533116</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>53.7</v>
+        <v>26.75</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>32.84609514892136</v>
+        <v>38.79252213082316</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.89584920167521</v>
+        <v>18.3091877474428</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.40681734293587</v>
+        <v>0.352590571254174</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.09555273722730639</v>
+        <v>-0.0780330140311286</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6931</v>
+        <v>6962</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>186.637618790594</v>
+        <v>193.4218228601752</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>38.8</v>
+        <v>32.45</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>34.59143375602321</v>
+        <v>34.51267856247044</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.00593488416312</v>
+        <v>17.67596239428818</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.297599077601938</v>
+        <v>0.8876050260739308</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0066757149945213</v>
+        <v>-0.6120074579245922</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6921</v>
+        <v>7547</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>183.2147658781094</v>
+        <v>188.7758645614698</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>53.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>33.14186460252019</v>
+        <v>32.84609514892136</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20.55927906440069</v>
+        <v>13.89584920167521</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.9038584636095476</v>
+        <v>1.40681734293587</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0568854861203276</v>
+        <v>-0.09555273722730639</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6908</v>
+        <v>6931</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>178.9908220937329</v>
+        <v>186.637618790594</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>35.6</v>
+        <v>38.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>31.66354505061206</v>
+        <v>34.59143375602321</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>20.4864602739698</v>
+        <v>14.00593488416312</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.416561287517466</v>
+        <v>1.297599077601938</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1084295866792164</v>
+        <v>-0.0066757149945213</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7803</v>
+        <v>6921</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>173.2124495553406</v>
+        <v>183.2147658781094</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>21.15</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>34.95381932449762</v>
+        <v>33.14186460252019</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>14.12687219790564</v>
+        <v>20.55927906440069</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>2.06225093682985</v>
+        <v>0.9038584636095476</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0166268277524717</v>
+        <v>0.0568854861203276</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>8044</v>
+        <v>6908</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>167.4022113911882</v>
+        <v>178.9908220937329</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>26.5</v>
+        <v>35.6</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>41.41839069403917</v>
+        <v>31.66354505061206</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.54053403933804</v>
+        <v>20.4864602739698</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.6565859163633775</v>
+        <v>1.416561287517466</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.2123122063754933</v>
+        <v>-0.1084295866792164</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6925</v>
+        <v>7803</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>162.4736879443008</v>
+        <v>173.2124495553406</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>54.1</v>
+        <v>21.15</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>34.21272545692831</v>
+        <v>34.95381932449762</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.15847396754973</v>
+        <v>14.12687219790564</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.921399533337081</v>
+        <v>2.06225093682985</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.4203058466257061</v>
+        <v>-0.0166268277524717</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6918</v>
+        <v>8044</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>156.5548242288912</v>
+        <v>167.4022113911882</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>26.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.3179031473957</v>
+        <v>41.41839069403917</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.57484812986517</v>
+        <v>13.54053403933804</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.357182615763852</v>
+        <v>0.6565859163633775</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1210166516609807</v>
+        <v>-0.2123122063754933</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6933</v>
+        <v>6925</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>140.077238116043</v>
+        <v>162.4736879443008</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>154</v>
+        <v>54.1</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.77638913030697</v>
+        <v>34.21272545692831</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.13624131502876</v>
+        <v>11.15847396754973</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.08979331030787</v>
+        <v>0.921399533337081</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>2.006323229942825</v>
+        <v>-0.4203058466257061</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6969</v>
+        <v>6918</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>121.8791254640136</v>
+        <v>156.5548242288912</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>24</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>40.42943543796945</v>
+        <v>38.3179031473957</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>19.94033968970785</v>
+        <v>15.57484812986517</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.9596668663663752</v>
+        <v>1.357182615763852</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0764636309237078</v>
+        <v>-0.1210166516609807</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7736</v>
+        <v>6933</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>113.8458565406949</v>
+        <v>140.077238116043</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>154</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.9157171415113</v>
+        <v>48.77638913030697</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.54633726606438</v>
+        <v>15.13624131502876</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.268161124800889</v>
+        <v>1.08979331030787</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0498325030266881</v>
+        <v>2.006323229942825</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>8011</v>
+        <v>6969</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>109.736551088585</v>
+        <v>121.8791254640136</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>16.25</v>
+        <v>24</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>34.25855100987837</v>
+        <v>40.42943543796945</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>19.25148739570474</v>
+        <v>19.94033968970785</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.08873225564897</v>
+        <v>0.9596668663663752</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.08424867206413959</v>
+        <v>0.0764636309237078</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6865</v>
+        <v>7736</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>97.17919962023498</v>
+        <v>113.8458565406949</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>25.4</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>49.64290976204602</v>
+        <v>41.9157171415113</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>12.43558849252515</v>
+        <v>17.54633726606438</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.8301558139158256</v>
+        <v>1.268161124800889</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,62 +7142,168 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1023503803957547</v>
+        <v>0.0498325030266881</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>8011</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>台通</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>109.736551088585</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>34.25855100987837</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>19.25148739570474</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>1.08873225564897</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.08424867206413959</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>6865</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>偉康科技</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>97.17919962023498</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>49.64290976204602</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>12.43558849252515</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.8301558139158256</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.1023503803957547</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>8038</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>長園科</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>80.68758344121653</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>37.5</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>41.71124119744621</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>19.01402503973465</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.5395731998575981</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>-0.2730660531070078</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
